--- a/ig/DM-AOUT-2026/CodeSystem-tre-r379-systeme-information.xlsx
+++ b/ig/DM-AOUT-2026/CodeSystem-tre-r379-systeme-information.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r379-systeme-information</t>
+    <t>http://hl7.org/fhir/us/example/CodeSystem/tre-r379-systeme-information</t>
   </si>
   <si>
     <t>Identifier</t>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260827120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-08-27T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -227,7 +227,7 @@
     <t>02</t>
   </si>
   <si>
-    <t>ARHGOS</t>
+    <t>SI-AUTORISATIONS</t>
   </si>
   <si>
     <t>03</t>

--- a/ig/DM-AOUT-2026/CodeSystem-tre-r379-systeme-information.xlsx
+++ b/ig/DM-AOUT-2026/CodeSystem-tre-r379-systeme-information.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/example/CodeSystem/tre-r379-systeme-information</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r379-systeme-information</t>
   </si>
   <si>
     <t>Identifier</t>
